--- a/testbuild/StructureDefinition-vkp-Observation-Bloodpressure.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-Bloodpressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.1</t>
+    <t>0.4.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -386,7 +386,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -522,7 +522,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -551,7 +551,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -631,7 +631,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -925,7 +925,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1134,7 +1134,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1212,7 +1212,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1300,7 +1300,7 @@
     <t>Observation.subject.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1340,7 +1340,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1363,7 +1363,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1596,7 +1596,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1628,7 +1628,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1788,7 +1788,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1816,7 +1816,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1896,7 +1896,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1946,7 +1946,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1982,7 +1982,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -2019,7 +2019,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2041,7 +2041,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2933,7 +2933,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.26171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4534,7 +4534,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>178</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>202</v>
       </c>
@@ -5136,7 +5136,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>217</v>
       </c>
@@ -5496,7 +5496,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>231</v>
       </c>
@@ -5738,7 +5738,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>249</v>
       </c>
@@ -6222,7 +6222,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>285</v>
       </c>
@@ -7668,7 +7668,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>322</v>
       </c>
@@ -8756,7 +8756,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>334</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>359</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>385</v>
       </c>
@@ -10078,7 +10078,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>395</v>
       </c>
@@ -10436,7 +10436,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>418</v>
       </c>
@@ -10798,7 +10798,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>440</v>
       </c>
@@ -11040,7 +11040,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>461</v>
       </c>
@@ -11638,7 +11638,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>474</v>
       </c>
@@ -12240,7 +12240,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>479</v>
       </c>
@@ -12360,7 +12360,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
         <v>481</v>
       </c>
@@ -12718,7 +12718,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>484</v>
       </c>
@@ -12958,7 +12958,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>497</v>
       </c>
@@ -13082,7 +13082,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
         <v>499</v>
       </c>
@@ -18486,7 +18486,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
         <v>664</v>
       </c>
@@ -18608,7 +18608,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="131" hidden="true">
+    <row r="131">
       <c r="A131" t="s" s="2">
         <v>670</v>
       </c>
@@ -18730,7 +18730,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
         <v>679</v>
       </c>
@@ -19096,7 +19096,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="135" hidden="true">
+    <row r="135">
       <c r="A135" t="s" s="2">
         <v>688</v>
       </c>
@@ -19580,7 +19580,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
         <v>693</v>
       </c>
@@ -21026,7 +21026,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
         <v>720</v>
       </c>
@@ -21388,7 +21388,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="154" hidden="true">
+    <row r="154">
       <c r="A154" t="s" s="2">
         <v>725</v>
       </c>
@@ -21630,7 +21630,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="156" hidden="true">
+    <row r="156">
       <c r="A156" t="s" s="2">
         <v>727</v>
       </c>
@@ -22114,7 +22114,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
         <v>733</v>
       </c>
@@ -22474,7 +22474,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="163" hidden="true">
+    <row r="163">
       <c r="A163" t="s" s="2">
         <v>738</v>
       </c>
@@ -22718,7 +22718,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="165" hidden="true">
+    <row r="165">
       <c r="A165" t="s" s="2">
         <v>759</v>
       </c>
@@ -22838,7 +22838,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="166" hidden="true">
+    <row r="166">
       <c r="A166" t="s" s="2">
         <v>767</v>
       </c>
@@ -22958,7 +22958,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="167" hidden="true">
+    <row r="167">
       <c r="A167" t="s" s="2">
         <v>776</v>
       </c>
@@ -23080,7 +23080,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="168" hidden="true">
+    <row r="168">
       <c r="A168" t="s" s="2">
         <v>784</v>
       </c>
@@ -23446,7 +23446,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="171" hidden="true">
+    <row r="171">
       <c r="A171" t="s" s="2">
         <v>787</v>
       </c>
@@ -23930,7 +23930,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="175" hidden="true">
+    <row r="175">
       <c r="A175" t="s" s="2">
         <v>792</v>
       </c>
@@ -25376,7 +25376,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="187" hidden="true">
+    <row r="187">
       <c r="A187" t="s" s="2">
         <v>808</v>
       </c>
@@ -25738,7 +25738,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="190" hidden="true">
+    <row r="190">
       <c r="A190" t="s" s="2">
         <v>813</v>
       </c>
@@ -25980,7 +25980,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="192" hidden="true">
+    <row r="192">
       <c r="A192" t="s" s="2">
         <v>815</v>
       </c>
@@ -26464,7 +26464,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="196" hidden="true">
+    <row r="196">
       <c r="A196" t="s" s="2">
         <v>820</v>
       </c>
@@ -26824,7 +26824,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="199" hidden="true">
+    <row r="199">
       <c r="A199" t="s" s="2">
         <v>823</v>
       </c>
@@ -27068,7 +27068,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="201" hidden="true">
+    <row r="201">
       <c r="A201" t="s" s="2">
         <v>825</v>
       </c>
@@ -27188,7 +27188,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="202" hidden="true">
+    <row r="202">
       <c r="A202" t="s" s="2">
         <v>826</v>
       </c>
@@ -27308,7 +27308,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="203" hidden="true">
+    <row r="203">
       <c r="A203" t="s" s="2">
         <v>827</v>
       </c>
@@ -27430,7 +27430,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="204" hidden="true">
+    <row r="204">
       <c r="A204" t="s" s="2">
         <v>828</v>
       </c>
@@ -27798,12 +27798,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP206">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/testbuild/StructureDefinition-vkp-Observation-Bloodpressure.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-Bloodpressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/testbuild/StructureDefinition-vkp-Observation-Bloodpressure.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-Bloodpressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.5.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/testbuild/StructureDefinition-vkp-Observation-Bloodpressure.xlsx
+++ b/testbuild/StructureDefinition-vkp-Observation-Bloodpressure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.1</t>
+    <t>0.5.2</t>
   </si>
   <si>
     <t>Name</t>
